--- a/output/output/aic_table.xlsx
+++ b/output/output/aic_table.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -425,20 +425,20 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C2" t="e">
-        <v>#N/A</v>
+      <c r="A2">
+        <v>45.8862999</v>
+      </c>
+      <c r="B2">
+        <v>26.87057081</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
       </c>
       <c r="D2" t="e">
         <v>#N/A</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6.5709677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -447,17 +447,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>832</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -468,38 +468,38 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>102.386258</v>
+        <v>32.72214184</v>
       </c>
       <c r="B3">
-        <v>64.96757301</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>9.92248237</v>
+        <v>24.24050116</v>
+      </c>
+      <c r="C3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D3" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E3">
-        <v>11.58607463</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>silvergray rockfish</t>
+          <t>blackbelly eelpout</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -510,91 +510,91 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>106.81843978</v>
+        <v>16.64975987</v>
       </c>
       <c r="B4">
-        <v>34.81860857</v>
-      </c>
-      <c r="C4">
-        <v>0.38040185</v>
-      </c>
-      <c r="D4">
-        <v>0.41301784</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="C4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>silvergray rockfish</t>
+          <t>blackbelly eelpout</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>49.66674237</v>
+      </c>
+      <c r="B5">
+        <v>40.46894304</v>
+      </c>
+      <c r="C5">
+        <v>3.03172672</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>3.64124608</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>blackbelly eelpout</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>coastwide</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>blackbelly eelpout</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>43.66728946</v>
+        <v>1.0660735</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -610,148 +610,148 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>blackbelly eelpout</t>
+          <t>redstripe rockfish</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6.04758847</v>
+      </c>
+      <c r="B7">
+        <v>2.52221411</v>
+      </c>
+      <c r="C7">
+        <v>4.91107126</v>
+      </c>
+      <c r="D7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>redstripe rockfish</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>blackbelly eelpout</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>28.26479277</v>
+      </c>
+      <c r="B8">
+        <v>17.68280815</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>5.8872697</v>
+      </c>
+      <c r="E8">
+        <v>5.39278365</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>redstripe rockfish</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>coastwide</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2950</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>redstripe rockfish</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>30.62243091</v>
-      </c>
-      <c r="B9">
-        <v>5.99776809</v>
-      </c>
-      <c r="C9">
-        <v>9.16012989</v>
-      </c>
-      <c r="D9">
-        <v>5.36651787</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="B9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E9" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>redstripe rockfish</t>
+          <t>lingcod</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -762,122 +762,122 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>74.31687938</v>
+        <v>15.55227609</v>
       </c>
       <c r="B10">
-        <v>42.11519661</v>
+        <v>14.89208778</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>16.27025491</v>
+        <v>5.16943827</v>
       </c>
       <c r="E10">
-        <v>16.32270545</v>
+        <v>4.26506052</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>redstripe rockfish</t>
+          <t>lingcod</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0.7720639</v>
+      </c>
+      <c r="E11">
+        <v>0.1752476</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>lingcod</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>coastwide</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2446</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>8.93003627</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>lingcod</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3428</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>5.13968593</v>
+        <v>0</v>
       </c>
       <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E12" t="e">
-        <v>#N/A</v>
+        <v>2.27460864</v>
+      </c>
+      <c r="C12">
+        <v>6.27460864</v>
+      </c>
+      <c r="D12">
+        <v>6.27460867</v>
+      </c>
+      <c r="E12">
+        <v>6.27460864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>lingcod</t>
+          <t>sharpchin rockfish</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>286</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -893,56 +893,56 @@
       <c r="B13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>2.37374638</v>
-      </c>
-      <c r="E13">
-        <v>1.71956942</v>
+      <c r="C13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>lingcod</t>
+          <t>sharpchin rockfish</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>431</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0</v>
+        <v>1.08407012</v>
       </c>
       <c r="B14">
-        <v>2.57519507</v>
-      </c>
-      <c r="C14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>2.77849328</v>
+      </c>
+      <c r="D14">
+        <v>32.48747865</v>
       </c>
       <c r="E14">
-        <v>3.73962866</v>
+        <v>2.71141476</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -951,185 +951,185 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>coastwide</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>27.35621502</v>
+      </c>
+      <c r="B15">
+        <v>15.3166998</v>
+      </c>
+      <c r="C15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yellowtail rockfish</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>cc</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>sharpchin rockfish</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>yellowtail rockfish</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>1.35582412</v>
-      </c>
-      <c r="B16">
-        <v>0.62668997</v>
-      </c>
-      <c r="C16">
-        <v>0.40006583</v>
-      </c>
-      <c r="D16">
-        <v>0.02925548</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>sharpchin rockfish</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>71.56098531</v>
+      </c>
+      <c r="B17">
+        <v>63.53056806</v>
+      </c>
+      <c r="C17">
+        <v>10.99110531</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>18.12463378</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yellowtail rockfish</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>coastwide</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>yellowtail rockfish</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>1.8080974</v>
+        <v>34.9638173</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>13.8358191</v>
       </c>
       <c r="C18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E18" t="e">
-        <v>#N/A</v>
+      <c r="D18">
+        <v>1.88410544</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yellowtail rockfish</t>
+          <t>pacific sanddab</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1140,211 +1140,211 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>149.81062283</v>
+        <v>27.75437862</v>
       </c>
       <c r="B19">
-        <v>125.68315934</v>
+        <v>27.98273673</v>
       </c>
       <c r="C19">
-        <v>15.50979961</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="D19" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E19">
-        <v>42.3521901</v>
+        <v>19.70342429</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yellowtail rockfish</t>
+          <t>pacific sanddab</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pacific sanddab</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>coastwide</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1610</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.68637491</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>3.9999982</v>
+      </c>
+      <c r="D21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>yelloweye rockfish</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>2.5121222</v>
+      </c>
+      <c r="C22">
+        <v>5.90915841</v>
+      </c>
+      <c r="D22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>yelloweye rockfish</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>yelloweye rockfish</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>coastwide</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>68.1496731</v>
-      </c>
-      <c r="B20">
-        <v>33.38064291</v>
-      </c>
-      <c r="C20">
-        <v>1.94409618</v>
-      </c>
-      <c r="D20">
-        <v>0.99829974</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>pacific sanddab</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3382</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>pacific sanddab</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>pacific sanddab</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4222</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>3.08540462</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D23">
-        <v>4.00000002</v>
-      </c>
-      <c r="E23">
-        <v>3.99999934</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>yelloweye rockfish</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       <c r="A24">
         <v>0</v>
       </c>
-      <c r="B24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C24">
-        <v>2.06677642</v>
-      </c>
-      <c r="D24">
-        <v>1.94554489</v>
-      </c>
-      <c r="E24">
-        <v>0.54710579</v>
+      <c r="B24">
+        <v>1.91830498</v>
+      </c>
+      <c r="C24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E24" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1371,17 +1371,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>195</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1392,19 +1392,19 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.3071241</v>
+        <v>0</v>
       </c>
       <c r="B25">
-        <v>0.05325758</v>
+        <v>3.2438846</v>
       </c>
       <c r="C25">
-        <v>1.76871699</v>
+        <v>5.78810465</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>5.63772312</v>
       </c>
       <c r="E25">
-        <v>3.73265388</v>
+        <v>5.01688188</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1413,40 +1413,40 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>0</v>
+        <v>2.84040788</v>
       </c>
       <c r="B26">
-        <v>1.00718644</v>
-      </c>
-      <c r="C26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E26" t="e">
-        <v>#N/A</v>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>1.44149873</v>
+      </c>
+      <c r="D26">
+        <v>1.26563481</v>
+      </c>
+      <c r="E26">
+        <v>0.61460073</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1455,17 +1455,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>cc _iphc</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1476,19 +1476,19 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0</v>
+        <v>5.43262289</v>
       </c>
       <c r="B27">
-        <v>1.30940236</v>
-      </c>
-      <c r="C27" t="e">
-        <v>#N/A</v>
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>2.86037845</v>
       </c>
       <c r="D27">
-        <v>2.09127909</v>
+        <v>9.43262061</v>
       </c>
       <c r="E27">
-        <v>1.22275224</v>
+        <v>4.0000001</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>bc _iphc</t>
+          <t>coastwide _iphc</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1512,44 +1512,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>12.43679223</v>
+        <v>32.51998009</v>
       </c>
       <c r="B28">
-        <v>5.70449412</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>3.8873932</v>
       </c>
       <c r="D28">
-        <v>0.25599194</v>
-      </c>
-      <c r="E28" t="e">
-        <v>#N/A</v>
+        <v>1.52671674</v>
+      </c>
+      <c r="E28">
+        <v>2.51760798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yelloweye rockfish</t>
+          <t>english sole</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>goa _iphc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1559,62 +1559,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>14.60067902</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
+      <c r="A29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B29" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C29">
-        <v>1.51200576</v>
-      </c>
-      <c r="D29">
-        <v>18.60067845</v>
+        <v>7.36663574</v>
+      </c>
+      <c r="D29" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E29">
-        <v>4.00000016</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yelloweye rockfish</t>
+          <t>english sole</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>coastwide _iphc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>868</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>55.22106158</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
+      <c r="A30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B30" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C30">
-        <v>3.90235814</v>
+        <v>0.19852124</v>
       </c>
       <c r="D30">
-        <v>1.02188445</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>2.3534068</v>
+        <v>0.05157419</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1623,17 +1623,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1649,11 +1649,11 @@
       <c r="B31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E31" t="e">
         <v>#N/A</v>
@@ -1665,59 +1665,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="e">
-        <v>#N/A</v>
+      <c r="A32">
+        <v>80.95364131</v>
       </c>
       <c r="B32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E32" t="e">
-        <v>#N/A</v>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>4.93800919</v>
+      </c>
+      <c r="E32">
+        <v>5.63447725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>english sole</t>
+          <t>petrale sole</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1736,161 +1736,161 @@
       <c r="C33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D33" t="e">
-        <v>#N/A</v>
+      <c r="D33">
+        <v>2.06607335</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>english sole</t>
+          <t>petrale sole</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>148.90365841</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0.8705396</v>
+      </c>
+      <c r="D34">
+        <v>0.71656541</v>
+      </c>
+      <c r="E34">
+        <v>0.88782255</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>petrale sole</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>coastwide</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B34">
-        <v>7.84232408</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>8.11451927</v>
-      </c>
-      <c r="E34">
-        <v>9.62645159</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>petrale sole</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>3.4571947</v>
+      </c>
+      <c r="C35">
+        <v>7.17368336</v>
+      </c>
+      <c r="D35">
+        <v>6.63090869</v>
+      </c>
+      <c r="E35">
+        <v>5.99696263</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>southern rock sole</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>cc</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>4342</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>petrale sole</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C36">
+        <v>5.53465041</v>
+      </c>
+      <c r="D36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>southern rock sole</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>279.84571122</v>
-      </c>
-      <c r="B36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>petrale sole</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>6292</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1904,11 +1904,11 @@
       <c r="C37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D37">
-        <v>6.10059476</v>
-      </c>
-      <c r="E37" t="e">
-        <v>#N/A</v>
+      <c r="D37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E37">
+        <v>4.63603268</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1917,166 +1917,166 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>goa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38">
+        <v>2.38720889</v>
+      </c>
+      <c r="C38">
+        <v>6.38653701</v>
+      </c>
+      <c r="D38">
+        <v>6.10068459</v>
+      </c>
+      <c r="E38">
+        <v>2.34777271</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>southern rock sole</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>coastwide</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>darkblotched rockfish</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>cc</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>southern rock sole</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E40">
+        <v>3.99999997</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>darkblotched rockfish</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>0</v>
-      </c>
-      <c r="B39">
-        <v>1.70818612</v>
-      </c>
-      <c r="C39">
-        <v>5.47594777</v>
-      </c>
-      <c r="D39">
-        <v>2.42534377</v>
-      </c>
-      <c r="E39">
-        <v>2.58464402</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>southern rock sole</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>goa</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>6.0033808</v>
-      </c>
-      <c r="B40">
-        <v>6.60879206</v>
-      </c>
-      <c r="C40">
-        <v>10.04046592</v>
-      </c>
-      <c r="D40">
-        <v>9.08579157</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>southern rock sole</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>33.7971466</v>
+        <v>28.47167984</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1.53755838</v>
       </c>
       <c r="C41">
-        <v>4.00000007</v>
-      </c>
-      <c r="D41">
-        <v>4.00000006</v>
+        <v>5.53755841</v>
+      </c>
+      <c r="D41" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E41">
-        <v>0.27998862</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2085,22 +2085,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2122,87 +2122,87 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>darkblotched rockfish</t>
+          <t>redbanded rockfish</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>2.17758938</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>redbanded rockfish</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>64.25699495</v>
-      </c>
-      <c r="B43">
-        <v>7.58291038</v>
-      </c>
-      <c r="C43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D43">
-        <v>3.38314681</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>darkblotched rockfish</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>0</v>
-      </c>
-      <c r="B44" t="e">
-        <v>#N/A</v>
+        <v>45.83712059</v>
+      </c>
+      <c r="B44">
+        <v>1.83677478</v>
       </c>
       <c r="C44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E44" t="e">
-        <v>#N/A</v>
+      <c r="D44">
+        <v>2.64397373</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2211,44 +2211,44 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="e">
-        <v>#N/A</v>
+      <c r="A45">
+        <v>9.16193447</v>
       </c>
       <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D45" t="e">
-        <v>#N/A</v>
+        <v>9.39136165</v>
+      </c>
+      <c r="C45">
+        <v>1.05232431</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>3.08177948</v>
+        <v>2.32099927</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>redbanded rockfish</t>
+          <t>big skate</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2276,21 +2276,21 @@
       <c r="A46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C46" t="e">
-        <v>#N/A</v>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>3.83650483</v>
       </c>
       <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>1.04297353</v>
+        <v>3.94180476</v>
+      </c>
+      <c r="E46" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>redbanded rockfish</t>
+          <t>big skate</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2318,21 +2318,21 @@
       <c r="A47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B47">
-        <v>0.16445295</v>
-      </c>
-      <c r="C47">
-        <v>3.8764497</v>
-      </c>
-      <c r="D47">
-        <v>4.16445301</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
+      <c r="B47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E47" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>redbanded rockfish</t>
+          <t>big skate</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2342,32 +2342,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>283</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B48" t="e">
-        <v>#N/A</v>
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48">
+        <v>1.99620868</v>
       </c>
       <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48" t="e">
-        <v>#N/A</v>
+        <v>1.44763667</v>
+      </c>
+      <c r="D48">
+        <v>1.23932364</v>
       </c>
       <c r="E48" t="e">
         <v>#N/A</v>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2405,14 +2405,14 @@
       <c r="B49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C49" t="e">
-        <v>#N/A</v>
+      <c r="C49">
+        <v>0</v>
       </c>
       <c r="D49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="E49" t="e">
-        <v>#N/A</v>
+      <c r="E49">
+        <v>0.76158393</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>486</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2441,14 +2441,14 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C50" t="e">
-        <v>#N/A</v>
+      <c r="A50">
+        <v>52.54589442</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>1.83409739</v>
       </c>
       <c r="D50" t="e">
         <v>#N/A</v>
@@ -2463,37 +2463,37 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D51" t="e">
-        <v>#N/A</v>
+      <c r="A51">
+        <v>44.13925326</v>
+      </c>
+      <c r="B51">
+        <v>13.23019104</v>
+      </c>
+      <c r="C51">
+        <v>4.31428103</v>
+      </c>
+      <c r="D51">
+        <v>28.63763277</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2505,59 +2505,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cc _iphc</t>
+          <t>coastwide _iphc</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>0</v>
-      </c>
-      <c r="B52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E52" t="e">
-        <v>#N/A</v>
+        <v>233.41993096</v>
+      </c>
+      <c r="B52">
+        <v>13.40053897</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>2.62191021</v>
+      </c>
+      <c r="E52">
+        <v>8.01196257</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>big skate</t>
+          <t>slender sole</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>bc _iphc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2567,8 +2567,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="e">
-        <v>#N/A</v>
+      <c r="A53">
+        <v>4.80645974</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2584,22 +2584,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>big skate</t>
+          <t>slender sole</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>goa _iphc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>975</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2609,123 +2609,123 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E54" t="e">
-        <v>#N/A</v>
+      <c r="A54">
+        <v>307.97822669</v>
+      </c>
+      <c r="B54">
+        <v>54.43199859</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1.63176841</v>
+      </c>
+      <c r="E54">
+        <v>6.94353115</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>big skate</t>
+          <t>slender sole</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ebs _iphc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>97.22159179</v>
+        <v>0</v>
       </c>
       <c r="B55">
-        <v>32.00217593</v>
+        <v>3.60823868</v>
       </c>
       <c r="C55">
-        <v>17.96278034</v>
-      </c>
-      <c r="D55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
+        <v>5.5513176</v>
+      </c>
+      <c r="D55">
+        <v>5.90704191</v>
+      </c>
+      <c r="E55" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>big skate</t>
+          <t>canary rockfish</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>coastwide _iphc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>393</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <v>482.69787343</v>
+      <c r="A56" t="e">
+        <v>#N/A</v>
       </c>
       <c r="B56">
-        <v>32.12991058</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
+        <v>5.70490519</v>
+      </c>
+      <c r="C56" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D56">
-        <v>7.46818144</v>
+        <v>0.87952023</v>
       </c>
       <c r="E56">
-        <v>15.53163123</v>
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>slender sole</t>
+          <t>canary rockfish</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>368</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2736,13 +2736,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>16.28138343</v>
+        <v>0.46079559</v>
       </c>
       <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57" t="e">
-        <v>#N/A</v>
+        <v>1.00688343</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
       </c>
       <c r="D57" t="e">
         <v>#N/A</v>
@@ -2752,106 +2752,106 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>slender sole</t>
+          <t>canary rockfish</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>762</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>611.41876477</v>
+        <v>57.69784584</v>
       </c>
       <c r="B58">
-        <v>109.96750068</v>
+        <v>13.51862074</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>2.97918888</v>
       </c>
       <c r="D58">
-        <v>3.01092472</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>14.3122144</v>
+        <v>2.67400684</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>slender sole</t>
+          <t>rex sole</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <v>0</v>
+      <c r="A59" t="e">
+        <v>#N/A</v>
       </c>
       <c r="B59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C59" t="e">
-        <v>#N/A</v>
+      <c r="C59">
+        <v>21.15234369</v>
       </c>
       <c r="D59">
-        <v>5.75853563</v>
-      </c>
-      <c r="E59" t="e">
-        <v>#N/A</v>
+        <v>21.19575349</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>canary rockfish</t>
+          <t>rex sole</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2862,38 +2862,38 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>36.14064778</v>
+        <v>0</v>
       </c>
       <c r="B60">
-        <v>26.6164426</v>
-      </c>
-      <c r="C60" t="e">
-        <v>#N/A</v>
+        <v>2.60366746</v>
+      </c>
+      <c r="C60">
+        <v>1.73346161</v>
       </c>
       <c r="D60">
-        <v>3.26120336</v>
+        <v>1.05004245</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>0.92922014</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>canary rockfish</t>
+          <t>rex sole</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>415</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -2904,13 +2904,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>3.05079425</v>
+        <v>1.74708027</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
-      <c r="C61">
-        <v>1.19552668</v>
+      <c r="C61" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D61" t="e">
         <v>#N/A</v>
@@ -2920,45 +2920,45 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>canary rockfish</t>
+          <t>rex sole</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>272</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>119.78719288</v>
+        <v>39.69308179</v>
       </c>
       <c r="B62">
-        <v>26.06074482</v>
+        <v>2.38231327</v>
       </c>
       <c r="C62">
-        <v>2.1551592</v>
+        <v>0.51292529</v>
       </c>
       <c r="D62">
-        <v>1.93525272</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>3.82636575</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2967,44 +2967,44 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63">
-        <v>177.62596326</v>
-      </c>
-      <c r="B63">
-        <v>79.85122122</v>
-      </c>
-      <c r="C63">
-        <v>45.16959859</v>
-      </c>
-      <c r="D63">
-        <v>43.67299871</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
+      <c r="A63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E63" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>rex sole</t>
+          <t>rougheye rockfish</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>407</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3029,24 +3029,24 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64">
-        <v>10.15230677</v>
-      </c>
-      <c r="B64">
-        <v>9.28428907</v>
+      <c r="A64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B64" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C64">
-        <v>2.03323726</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64">
-        <v>1.63800431</v>
+        <v>0</v>
+      </c>
+      <c r="D64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E64" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>rex sole</t>
+          <t>rougheye rockfish</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3080,77 +3080,77 @@
       <c r="C65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D65">
-        <v>1.13695422</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
+      <c r="D65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E65" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>rex sole</t>
+          <t>rougheye rockfish</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>87.34171674</v>
+        <v>4.19452655</v>
       </c>
       <c r="B66">
-        <v>7.78011655</v>
-      </c>
-      <c r="C66">
-        <v>0.9697944</v>
+        <v>0</v>
+      </c>
+      <c r="C66" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>7.46438723</v>
+        <v>4</v>
+      </c>
+      <c r="E66" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>rex sole</t>
+          <t>rougheye rockfish</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3206,8 +3206,8 @@
       <c r="C68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D68" t="e">
-        <v>#N/A</v>
+      <c r="D68">
+        <v>1.3170718</v>
       </c>
       <c r="E68" t="e">
         <v>#N/A</v>
@@ -3219,311 +3219,311 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>goa _iphc</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>6.39230209</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>3.26818462</v>
+      </c>
+      <c r="D69">
+        <v>10.39230214</v>
+      </c>
+      <c r="E69">
+        <v>4.00000003</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>rougheye rockfish</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>coastwide _iphc</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>spotted ratfish</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2438</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>86.14374367</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E71">
+        <v>3.13142643</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>spotted ratfish</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E69">
-        <v>3.22538892</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>rougheye rockfish</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>128.02754269</v>
+      </c>
+      <c r="B72">
+        <v>7.04829403</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>1.04685309</v>
+      </c>
+      <c r="E72">
+        <v>1.29265484</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>spotted ratfish</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>coastwide</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>4033</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>6.47453217</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D73">
+        <v>1.78877265</v>
+      </c>
+      <c r="E73">
+        <v>1.95289697</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>arrowtooth flounder</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B74">
+        <v>22.04182446</v>
+      </c>
+      <c r="C74">
+        <v>11.84301388</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>arrowtooth flounder</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0</v>
+      </c>
+      <c r="B75">
+        <v>0.35404988</v>
+      </c>
+      <c r="C75">
+        <v>1.21087653</v>
+      </c>
+      <c r="D75">
+        <v>1.96823231</v>
+      </c>
+      <c r="E75">
+        <v>3.80219029</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>arrowtooth flounder</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>goa</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>0</v>
-      </c>
-      <c r="B70">
-        <v>3.96108465</v>
-      </c>
-      <c r="C70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>rougheye rockfish</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>rougheye rockfish</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>cc _iphc</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>rougheye rockfish</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>bc _iphc</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>rougheye rockfish</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>goa _iphc</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>15.80845671</v>
-      </c>
-      <c r="B74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>rougheye rockfish</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>coastwide _iphc</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>spotted ratfish</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>4876</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3534,33 +3534,33 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>180.88596139</v>
+        <v>25.59240321</v>
       </c>
       <c r="B76">
-        <v>1.16232027</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>3.57347299</v>
+        <v>4.00000003</v>
+      </c>
+      <c r="D76" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E76">
-        <v>3.87523424</v>
+        <v>4.00000002</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>spotted ratfish</t>
+          <t>arrowtooth flounder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3576,23 +3576,23 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>266.66239114</v>
+        <v>40.10944929</v>
       </c>
       <c r="B77">
-        <v>19.45275387</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1.59469781</v>
       </c>
       <c r="D77">
-        <v>3.060159</v>
+        <v>2.94304392</v>
       </c>
       <c r="E77" t="e">
         <v>#N/A</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>spotted ratfish</t>
+          <t>arrowtooth flounder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3612,29 +3612,29 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>15.09742529</v>
+        <v>90.8011635</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
-      <c r="C78">
-        <v>4.0000001</v>
-      </c>
-      <c r="D78">
-        <v>0.47140814</v>
-      </c>
-      <c r="E78">
-        <v>0.00548312</v>
+      <c r="C78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E78" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>arrowtooth flounder</t>
+          <t>pacific hake</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3659,24 +3659,24 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
-        <v>252.21477771</v>
+      <c r="A79" t="e">
+        <v>#N/A</v>
       </c>
       <c r="B79">
-        <v>47.90656856</v>
+        <v>30.67051312</v>
       </c>
       <c r="C79">
-        <v>24.87663673</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>2.59954061</v>
       </c>
       <c r="E79" t="e">
         <v>#N/A</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>arrowtooth flounder</t>
+          <t>pacific hake</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>663</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3701,81 +3701,81 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B80" t="e">
-        <v>#N/A</v>
+      <c r="A80">
+        <v>29.60211529</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
       </c>
       <c r="C80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D80">
-        <v>0</v>
+      <c r="D80" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E80" t="e">
         <v>#N/A</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>arrowtooth flounder</t>
+          <t>pacific hake</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>61.6042027</v>
+        <v>3.59093744</v>
       </c>
       <c r="B81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C81" t="e">
-        <v>#N/A</v>
+      <c r="C81">
+        <v>1.52233857</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0.02176812</v>
+        <v>0.03829722</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>arrowtooth flounder</t>
+          <t>flathead sole</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3786,80 +3786,80 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>81.20214593</v>
+        <v>13.2942058</v>
       </c>
       <c r="B82">
-        <v>1.76897498</v>
+        <v>0.61384386</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.66913637</v>
       </c>
       <c r="D82">
-        <v>2.85543992</v>
+        <v>0</v>
       </c>
       <c r="E82" t="e">
         <v>#N/A</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>arrowtooth flounder</t>
+          <t>flathead sole</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>752</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="e">
-        <v>#N/A</v>
+      <c r="A83">
+        <v>0</v>
       </c>
       <c r="B83">
-        <v>125.25814643</v>
+        <v>3.1628418</v>
       </c>
       <c r="C83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D83" t="e">
-        <v>#N/A</v>
+      <c r="D83">
+        <v>7.1628418</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>7.16283573</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>pacific hake</t>
+          <t>flathead sole</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>443</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3869,34 +3869,34 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="e">
-        <v>#N/A</v>
+      <c r="A84">
+        <v>0</v>
       </c>
       <c r="B84">
-        <v>64.46012949</v>
+        <v>0.63512953</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>2.9176948</v>
       </c>
       <c r="D84">
-        <v>7.62367586</v>
+        <v>3.48914322</v>
       </c>
       <c r="E84">
-        <v>1.01488572</v>
+        <v>2.93455616</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>pacific hake</t>
+          <t>flathead sole</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>815</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3912,23 +3912,23 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>56.62992202</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
+        <v>14.30079106</v>
+      </c>
+      <c r="B85" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D85" t="e">
-        <v>#N/A</v>
+      <c r="D85">
+        <v>0</v>
       </c>
       <c r="E85" t="e">
         <v>#N/A</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>pacific hake</t>
+          <t>flathead sole</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3948,29 +3948,29 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>6.33729889</v>
+        <v>75.42843244</v>
       </c>
       <c r="B86">
-        <v>8.07155977</v>
-      </c>
-      <c r="C86" t="e">
-        <v>#N/A</v>
+        <v>7.13212056</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86" t="e">
-        <v>#N/A</v>
+        <v>2.35378225</v>
+      </c>
+      <c r="E86">
+        <v>7.74706373</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>flathead sole</t>
+          <t>longnose skate</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3996,23 +3996,23 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>56.83792513</v>
-      </c>
-      <c r="B87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C87">
-        <v>19.80997733</v>
+        <v>0</v>
+      </c>
+      <c r="B87">
+        <v>3.73353134</v>
+      </c>
+      <c r="C87" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="E87">
-        <v>0</v>
+      <c r="E87" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>flathead sole</t>
+          <t>longnose skate</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>608</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4038,80 +4038,80 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0</v>
+        <v>94.23974431</v>
       </c>
       <c r="B88">
-        <v>2.07151107</v>
-      </c>
-      <c r="C88" t="e">
-        <v>#N/A</v>
+        <v>18.28290926</v>
+      </c>
+      <c r="C88">
+        <v>10.78308574</v>
       </c>
       <c r="D88">
-        <v>5.83901531</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>6.0715111</v>
+        <v>4.45148002</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>flathead sole</t>
+          <t>longnose skate</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>6.4220066</v>
+        <v>67.6472827</v>
       </c>
       <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="C89">
-        <v>1.64661308</v>
+        <v>17.93986411</v>
+      </c>
+      <c r="C89" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D89">
-        <v>2.75441073</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>0.76824801</v>
+        <v>13.04635334</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>flathead sole</t>
+          <t>longnose skate</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4121,44 +4121,44 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B90" t="e">
-        <v>#N/A</v>
+      <c r="A90">
+        <v>5.18089255</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>3.50328637</v>
       </c>
       <c r="D90">
-        <v>2.12203776</v>
-      </c>
-      <c r="E90" t="e">
-        <v>#N/A</v>
+        <v>3.95147047</v>
+      </c>
+      <c r="E90">
+        <v>3.81481873</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>flathead sole</t>
+          <t>longnose skate</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4169,11 +4169,11 @@
       <c r="B91" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E91" t="e">
         <v>#N/A</v>
@@ -4185,17 +4185,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4206,19 +4206,19 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>5.14170566</v>
-      </c>
-      <c r="B92" t="e">
-        <v>#N/A</v>
+        <v>180.00678027</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
       </c>
       <c r="C92" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="E92">
-        <v>3.62201322</v>
+      <c r="D92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E92" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4227,70 +4227,70 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>coastwide _iphc</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>181.90623579</v>
+        <v>18.45080982</v>
       </c>
       <c r="B93">
-        <v>38.95947425</v>
+        <v>17.50604578</v>
       </c>
       <c r="C93">
-        <v>20.51813019</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1.11237054</v>
       </c>
       <c r="E93">
-        <v>8.35948346</v>
+        <v>1.7700344</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>longnose skate</t>
+          <t>pacific halibut</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>95.44796155</v>
+        <v>0.57116148</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -4301,27 +4301,27 @@
       <c r="D94" t="e">
         <v>#N/A</v>
       </c>
-      <c r="E94" t="e">
-        <v>#N/A</v>
+      <c r="E94">
+        <v>0.18098562</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>longnose skate</t>
+          <t>pacific halibut</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>cc _iphc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>658</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4332,38 +4332,38 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>18.96468101</v>
+        <v>0</v>
       </c>
       <c r="B95">
-        <v>0</v>
-      </c>
-      <c r="C95">
-        <v>2.79668806</v>
-      </c>
-      <c r="D95">
-        <v>3.93883322</v>
-      </c>
-      <c r="E95">
-        <v>3.54433749</v>
+        <v>2.15633338</v>
+      </c>
+      <c r="C95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E95" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>longnose skate</t>
+          <t>pacific halibut</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>bc _iphc</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4374,38 +4374,38 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>72.30257932</v>
+        <v>0</v>
       </c>
       <c r="B96">
-        <v>1.0022804</v>
+        <v>3.84266682</v>
       </c>
       <c r="C96">
-        <v>0</v>
-      </c>
-      <c r="D96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E96" t="e">
-        <v>#N/A</v>
+        <v>2.52539045</v>
+      </c>
+      <c r="D96">
+        <v>1.95837499</v>
+      </c>
+      <c r="E96">
+        <v>3.23352008</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>longnose skate</t>
+          <t>pacific halibut</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>goa _iphc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4416,61 +4416,61 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>338.54768719</v>
+        <v>7.37604316</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-      <c r="C97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E97" t="e">
-        <v>#N/A</v>
+        <v>1.29552621</v>
+      </c>
+      <c r="C97">
+        <v>1.84734526</v>
+      </c>
+      <c r="D97">
+        <v>1.21188703</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>longnose skate</t>
+          <t>pacific halibut</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>coastwide _iphc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="e">
-        <v>#N/A</v>
+      <c r="A98">
+        <v>74.52998875</v>
       </c>
       <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="C98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E98" t="e">
-        <v>#N/A</v>
+        <v>68.3850241</v>
+      </c>
+      <c r="C98">
+        <v>4.43175448</v>
+      </c>
+      <c r="D98">
+        <v>2.62362539</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4479,17 +4479,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>982</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4500,19 +4500,19 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>13.70994688</v>
+        <v>54.49365279</v>
       </c>
       <c r="B99">
-        <v>8.59818147</v>
+        <v>45.5416017</v>
       </c>
       <c r="C99">
-        <v>0.85568155</v>
+        <v>11.69251503</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>3.365378</v>
       </c>
       <c r="E99">
-        <v>1.80181192</v>
+        <v>0</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4521,17 +4521,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4541,20 +4541,20 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E100" t="e">
-        <v>#N/A</v>
+      <c r="A100">
+        <v>34.14846267</v>
+      </c>
+      <c r="B100">
+        <v>15.81838057</v>
+      </c>
+      <c r="C100">
+        <v>4.63631048</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>3.59098009</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -4584,19 +4584,19 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>5.01633323</v>
+        <v>33.57220706</v>
       </c>
       <c r="B101">
-        <v>5.16445983</v>
-      </c>
-      <c r="C101">
-        <v>2.68070424</v>
+        <v>7.09938262</v>
+      </c>
+      <c r="C101" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>4.01951803</v>
+        <v>6.697493</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4605,17 +4605,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>ebs _iphc</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -4626,16 +4626,16 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>22.84561527</v>
+        <v>60.22703631</v>
       </c>
       <c r="B102">
-        <v>5.33685784</v>
+        <v>30.24209034</v>
       </c>
       <c r="C102">
-        <v>2.74072671</v>
+        <v>1.51742299</v>
       </c>
       <c r="D102">
-        <v>1.41188658</v>
+        <v>45.27258263</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4647,17 +4647,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>coastwide _iphc</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4668,38 +4668,38 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>144.86446058</v>
+        <v>38.57209614</v>
       </c>
       <c r="B103">
-        <v>122.27350294</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>6.07148139</v>
+        <v>3.65661673</v>
       </c>
       <c r="D103">
-        <v>4.27033937</v>
+        <v>4.0293182</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>3.33115326</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>pacific halibut</t>
+          <t>spiny dogfish</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>cc _iphc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>926</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -4709,39 +4709,39 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104">
-        <v>138.42967375</v>
+      <c r="A104" t="e">
+        <v>#N/A</v>
       </c>
       <c r="B104">
-        <v>101.85612627</v>
-      </c>
-      <c r="C104">
-        <v>23.48000323</v>
+        <v>0</v>
+      </c>
+      <c r="C104" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D104">
-        <v>6.18420703</v>
-      </c>
-      <c r="E104">
-        <v>0</v>
+        <v>3.99999973</v>
+      </c>
+      <c r="E104" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>pacific halibut</t>
+          <t>spiny dogfish</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>bc _iphc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>823</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -4752,75 +4752,75 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>84.73119794</v>
+        <v>117.92089789</v>
       </c>
       <c r="B105">
-        <v>42.21690285</v>
+        <v>59.10627107</v>
       </c>
       <c r="C105">
-        <v>8.54254752</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105">
-        <v>5.08944775</v>
+        <v>21.12316928</v>
+      </c>
+      <c r="E105" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>pacific halibut</t>
+          <t>spiny dogfish</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>goa _iphc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="e">
-        <v>#N/A</v>
+      <c r="A106">
+        <v>32.09491904</v>
       </c>
       <c r="B106">
-        <v>17.36067613</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>10.29146751</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
+        <v>1.14948004</v>
+      </c>
+      <c r="D106" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E106">
-        <v>15.67678745</v>
+        <v>3.41667661</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>pacific halibut</t>
+          <t>spiny dogfish</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ebs _iphc</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4835,34 +4835,34 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="e">
-        <v>#N/A</v>
+      <c r="A107">
+        <v>60.73492069</v>
       </c>
       <c r="B107">
-        <v>63.60347146</v>
+        <v>3.34348257</v>
       </c>
       <c r="C107">
-        <v>3.24874032</v>
+        <v>1.76894949</v>
       </c>
       <c r="D107">
-        <v>97.67721844</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>0.03231139</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>pacific halibut</t>
+          <t>spiny dogfish</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>coastwide _iphc</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4872,25 +4872,25 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>97.17200645</v>
+        <v>53.9858963</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>4.00000012</v>
+        <v>4.00000021</v>
       </c>
       <c r="D108">
-        <v>1.96960345</v>
+        <v>3.226265</v>
       </c>
       <c r="E108">
-        <v>1.52995159</v>
+        <v>4.00000014</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4899,17 +4899,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4920,19 +4920,19 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>94.68999374</v>
+        <v>191.68917015</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>1.48985568</v>
       </c>
       <c r="C109">
-        <v>4.00000003</v>
-      </c>
-      <c r="D109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E109" t="e">
-        <v>#N/A</v>
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>192.45885348</v>
+      </c>
+      <c r="E109">
+        <v>22.06514803</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4941,143 +4941,143 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
+          <t>coastwide _iphc</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>6736</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>20.98036432</v>
+      </c>
+      <c r="B110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0.63741185</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>pacific cod</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>15.03230097</v>
+      </c>
+      <c r="B111">
+        <v>16.78481727</v>
+      </c>
+      <c r="C111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>pacific cod</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1646</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>spiny dogfish</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B112">
+        <v>0.03180146</v>
+      </c>
+      <c r="C112">
+        <v>2.44824182</v>
+      </c>
+      <c r="D112">
+        <v>1.60930909</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>pacific cod</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>goa</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C111">
-        <v>0</v>
-      </c>
-      <c r="D111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E111">
-        <v>40.55596584</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>spiny dogfish</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112">
-        <v>60.3779698</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-      <c r="C112">
-        <v>1.54359535</v>
-      </c>
-      <c r="D112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>spiny dogfish</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>cc _iphc</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5088,38 +5088,38 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>134.57243391</v>
+        <v>0</v>
       </c>
       <c r="B113">
-        <v>15.03069416</v>
-      </c>
-      <c r="C113">
-        <v>4.66198893</v>
-      </c>
-      <c r="D113">
-        <v>0.60789156</v>
-      </c>
-      <c r="E113">
-        <v>0</v>
+        <v>1.7085545</v>
+      </c>
+      <c r="C113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E113" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>spiny dogfish</t>
+          <t>pacific cod</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>bc _iphc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5130,103 +5130,103 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>84.89177353</v>
-      </c>
-      <c r="B114" t="e">
-        <v>#N/A</v>
+        <v>23.92184052</v>
+      </c>
+      <c r="B114">
+        <v>19.01658766</v>
       </c>
       <c r="C114">
-        <v>2.23057662</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
-      </c>
-      <c r="E114" t="e">
-        <v>#N/A</v>
+        <v>1.08627288</v>
+      </c>
+      <c r="E114">
+        <v>0.421847</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>spiny dogfish</t>
+          <t>pacific cod</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>goa _iphc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>383.01593676</v>
+        <v>29.87380112</v>
       </c>
       <c r="B115">
-        <v>7.85155807</v>
+        <v>32.1461916</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>0.49406184</v>
       </c>
       <c r="D115">
-        <v>379.9867555</v>
+        <v>0</v>
       </c>
       <c r="E115" t="e">
         <v>#N/A</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>spiny dogfish</t>
+          <t>pacific cod</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>coastwide _iphc</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>269</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>47.47594395</v>
+        <v>0</v>
       </c>
       <c r="B116">
-        <v>51.29744626</v>
-      </c>
-      <c r="C116" t="e">
-        <v>#N/A</v>
+        <v>3.03476785</v>
+      </c>
+      <c r="C116">
+        <v>3.54679001</v>
       </c>
       <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116" t="e">
-        <v>#N/A</v>
+        <v>3.71424781</v>
+      </c>
+      <c r="E116">
+        <v>2.88392769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5235,17 +5235,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>951</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5255,20 +5255,20 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D117">
-        <v>3.22449215</v>
+      <c r="A117">
+        <v>192.0827512</v>
+      </c>
+      <c r="B117">
+        <v>84.10600914</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>2.24883339</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5277,17 +5277,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -5303,14 +5303,14 @@
       <c r="B118" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C118">
-        <v>0</v>
-      </c>
-      <c r="D118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E118" t="e">
-        <v>#N/A</v>
+      <c r="C118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D118">
+        <v>6.08148909</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5319,17 +5319,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>ebs _iphc</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -5340,19 +5340,19 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>3.38773011</v>
+        <v>236.55351966</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>113.14554613</v>
       </c>
       <c r="C119">
-        <v>4.00000007</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>4.00000002</v>
+        <v>174.46856423</v>
       </c>
       <c r="E119">
-        <v>4.00000006</v>
+        <v>4.88393562</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5361,76 +5361,76 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>coastwide _iphc</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>52.93629206</v>
+        <v>23.80711685</v>
       </c>
       <c r="B120">
-        <v>39.56716095</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>2.96812732</v>
       </c>
       <c r="D120">
-        <v>2.0282175</v>
+        <v>4.00000002</v>
       </c>
       <c r="E120">
-        <v>0.43531443</v>
+        <v>4.00000001</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>pacific cod</t>
+          <t>walleye pollock</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121">
-        <v>71.87040791</v>
+      <c r="A121" t="e">
+        <v>#N/A</v>
       </c>
       <c r="B121">
-        <v>73.35994053</v>
-      </c>
-      <c r="C121" t="e">
-        <v>#N/A</v>
+        <v>9.79173411</v>
+      </c>
+      <c r="C121">
+        <v>3.24392345</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -5440,22 +5440,22 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>pacific cod</t>
+          <t>walleye pollock</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>cc _iphc</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -5466,38 +5466,38 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>4.52659769</v>
+        <v>0</v>
       </c>
       <c r="B122">
-        <v>5.86903941</v>
+        <v>0.05468729</v>
       </c>
       <c r="C122">
-        <v>0</v>
-      </c>
-      <c r="D122">
-        <v>1.52086769</v>
-      </c>
-      <c r="E122" t="e">
-        <v>#N/A</v>
+        <v>2.68734457</v>
+      </c>
+      <c r="D122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E122">
+        <v>2.87276191</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>pacific cod</t>
+          <t>walleye pollock</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>bc _iphc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -5508,80 +5508,80 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>381.2112458</v>
+        <v>38.01551098</v>
       </c>
       <c r="B123">
-        <v>173.70814672</v>
-      </c>
-      <c r="C123" t="e">
-        <v>#N/A</v>
+        <v>9.97503483</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>3.84414169</v>
       </c>
       <c r="E123">
-        <v>2.20865133</v>
+        <v>4.95922796</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>pacific cod</t>
+          <t>walleye pollock</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>goa _iphc</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>94.59684305</v>
-      </c>
-      <c r="B124" t="e">
-        <v>#N/A</v>
+        <v>310.02412603</v>
+      </c>
+      <c r="B124">
+        <v>3.02077725</v>
       </c>
       <c r="C124">
-        <v>19.12430789</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>12.41349247</v>
+        <v>2.10732399</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>5.17680587</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>pacific cod</t>
+          <t>dover sole</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ebs _iphc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -5592,159 +5592,159 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>474.47163526</v>
+        <v>26.60479872</v>
       </c>
       <c r="B125">
-        <v>226.28861201</v>
-      </c>
-      <c r="C125">
-        <v>0</v>
-      </c>
-      <c r="D125">
-        <v>347.96375099</v>
-      </c>
-      <c r="E125">
-        <v>9.62930429</v>
+        <v>0</v>
+      </c>
+      <c r="C125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E125" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>pacific cod</t>
+          <t>dover sole</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>coastwide _iphc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>63.31514092</v>
+        <v>0</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>3.96508778</v>
       </c>
       <c r="C126">
-        <v>1.28850959</v>
+        <v>7.20912636</v>
       </c>
       <c r="D126">
-        <v>4</v>
+        <v>7.84500952</v>
       </c>
       <c r="E126">
-        <v>3.74625628</v>
+        <v>7.94228184</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>walleye pollock</t>
+          <t>dover sole</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
+          <t>goa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>7.66836765</v>
+      </c>
+      <c r="E127">
+        <v>17.80927101</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>dover sole</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>coastwide</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>bering skate</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127">
-        <v>29.8149933</v>
-      </c>
-      <c r="B127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="E127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>walleye pollock</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>goa</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128">
-        <v>0</v>
-      </c>
-      <c r="B128">
-        <v>1.07102994</v>
-      </c>
-      <c r="C128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E128">
-        <v>3.81710251</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>walleye pollock</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>ebs</t>
-        </is>
-      </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>238</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5760,80 +5760,80 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>81.75314305</v>
+        <v>0</v>
       </c>
       <c r="B129">
-        <v>24.84168164</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>7.68503489</v>
-      </c>
-      <c r="E129">
-        <v>9.40748806</v>
+        <v>2.11995151</v>
+      </c>
+      <c r="C129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E129" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>walleye pollock</t>
+          <t>bering skate</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>628.92002755</v>
+        <v>1.42434166</v>
       </c>
       <c r="B130">
-        <v>8.31176033</v>
-      </c>
-      <c r="C130" t="e">
-        <v>#N/A</v>
+        <v>1.3684229</v>
+      </c>
+      <c r="C130">
+        <v>5.36841991</v>
       </c>
       <c r="D130">
-        <v>0</v>
-      </c>
-      <c r="E130" t="e">
-        <v>#N/A</v>
+        <v>3.52873735</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>dover sole</t>
+          <t>bering skate</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>297</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -5844,117 +5844,117 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>134.01637744</v>
+        <v>11.27736106</v>
       </c>
       <c r="B131">
-        <v>53.12911164</v>
-      </c>
-      <c r="C131">
-        <v>26.95694988</v>
+        <v>7.2628535</v>
+      </c>
+      <c r="C131" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D131">
-        <v>21.8123681</v>
+        <v>0.56660815</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>dover sole</t>
+          <t>bering skate</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
+          <t>coastwide</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>shortspine thornyhead</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>33.362604</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D133">
+        <v>4.00000001</v>
+      </c>
+      <c r="E133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>shortspine thornyhead</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132">
-        <v>0</v>
-      </c>
-      <c r="B132">
-        <v>3.2972858</v>
-      </c>
-      <c r="C132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E132">
-        <v>6.91085039</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>dover sole</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>goa</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>dover sole</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>ebs</t>
-        </is>
-      </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>643</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5970,75 +5970,75 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>595.80650475</v>
+        <v>0</v>
       </c>
       <c r="B134">
-        <v>43.28074613</v>
+        <v>3.03160957</v>
       </c>
       <c r="C134">
-        <v>11.70001385</v>
+        <v>6.08886377</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>5.72433376</v>
       </c>
       <c r="E134">
-        <v>9.06503214</v>
+        <v>5.84364116</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>dover sole</t>
+          <t>shortspine thornyhead</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="e">
-        <v>#N/A</v>
+      <c r="A135">
+        <v>48.35846649</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>27.58258026</v>
       </c>
       <c r="C135" t="e">
         <v>#N/A</v>
       </c>
-      <c r="D135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E135" t="e">
-        <v>#N/A</v>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>2.3762333</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>bering skate</t>
+          <t>shortspine thornyhead</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>ebs</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>205</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6054,80 +6054,80 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>0.19178399</v>
+        <v>183.12904453</v>
       </c>
       <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136" t="e">
-        <v>#N/A</v>
+        <v>98.6974916</v>
+      </c>
+      <c r="C136">
+        <v>27.17728742</v>
       </c>
       <c r="D136">
-        <v>2.36193818</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>3.23844179</v>
+        <v>18.78996132</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>bering skate</t>
+          <t>shortspine thornyhead</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>goa</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="e">
-        <v>#N/A</v>
+      <c r="A137">
+        <v>14.97129344</v>
       </c>
       <c r="B137">
-        <v>0.68820173</v>
-      </c>
-      <c r="C137">
-        <v>4.68820174</v>
+        <v>0</v>
+      </c>
+      <c r="C137" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="E137" t="e">
-        <v>#N/A</v>
+        <v>4.00000007</v>
+      </c>
+      <c r="E137">
+        <v>4.00000007</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>bering skate</t>
+          <t>longspine thornyhead</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6138,80 +6138,80 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>30.04618894</v>
+        <v>68.42563177</v>
       </c>
       <c r="B138">
-        <v>20.45886861</v>
-      </c>
-      <c r="C138">
-        <v>2.95294175</v>
+        <v>58.50659846</v>
+      </c>
+      <c r="C138" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D138">
-        <v>1.104133</v>
+        <v>31.01314446</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>bering skate</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D139" t="e">
-        <v>#N/A</v>
+      <c r="A139">
+        <v>55.86372789</v>
+      </c>
+      <c r="B139">
+        <v>26.2381858</v>
+      </c>
+      <c r="C139">
+        <v>12.68826518</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
       </c>
       <c r="E139" t="e">
         <v>#N/A</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>shortspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6224,78 +6224,78 @@
       <c r="A140" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B140">
-        <v>1.62972972</v>
-      </c>
-      <c r="C140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E140">
-        <v>0</v>
+      <c r="B140" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0.1421511</v>
+      </c>
+      <c r="E140" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>shortspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>goa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>29.66780066</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>sablefish</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ebs</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C141">
-        <v>1.00278154</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="E141">
-        <v>0.25641394</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>shortspine thornyhead</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>goa</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6306,10 +6306,10 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>102.39732092</v>
+        <v>147.95018486</v>
       </c>
       <c r="B142">
-        <v>57.43042375</v>
+        <v>139.49192494</v>
       </c>
       <c r="C142" t="e">
         <v>#N/A</v>
@@ -6317,111 +6317,111 @@
       <c r="D142">
         <v>0</v>
       </c>
-      <c r="E142" t="e">
-        <v>#N/A</v>
+      <c r="E142">
+        <v>48.54553957</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>shortspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ebs</t>
+          <t>coastwide</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>360.50423103</v>
+        <v>0</v>
       </c>
       <c r="B143">
-        <v>184.36669756</v>
-      </c>
-      <c r="C143">
-        <v>48.54280427</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-      <c r="E143">
-        <v>36.27033242</v>
+        <v>3.14982016</v>
+      </c>
+      <c r="C143" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D143" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E143" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>shortspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>cc _iphc</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>23.15693433</v>
+        <v>53.65508453</v>
       </c>
       <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D144" t="e">
-        <v>#N/A</v>
+        <v>17.13520693</v>
+      </c>
+      <c r="C144">
+        <v>8.13892552</v>
+      </c>
+      <c r="D144">
+        <v>3.49588874</v>
       </c>
       <c r="E144">
-        <v>4.00000014</v>
+        <v>0</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>longspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc _iphc</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6431,39 +6431,39 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E145" t="e">
-        <v>#N/A</v>
+      <c r="A145">
+        <v>84.66620039</v>
+      </c>
+      <c r="B145">
+        <v>87.5617193</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>23.59092759</v>
+      </c>
+      <c r="E145">
+        <v>17.13264545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>longspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>goa _iphc</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -6473,62 +6473,62 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146">
-        <v>55.49119781</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
+      <c r="A146" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B146" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C146" t="e">
         <v>#N/A</v>
       </c>
       <c r="D146">
-        <v>4.00000021</v>
-      </c>
-      <c r="E146">
-        <v>4.00000012</v>
+        <v>0</v>
+      </c>
+      <c r="E146" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>longspine thornyhead</t>
+          <t>sablefish</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>coastwide</t>
+          <t>ebs _iphc</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>102.30865236</v>
+        <v>279.9142525</v>
       </c>
       <c r="B147">
-        <v>89.18764969</v>
+        <v>254.01138652</v>
       </c>
       <c r="C147">
-        <v>28.2647325</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>46.28560251</v>
+        <v>49.16479517</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>24.40426706</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6537,398 +6537,20 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>coastwide _iphc</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C148">
-        <v>3.98908072</v>
-      </c>
-      <c r="D148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E148">
-        <v>0</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>2374</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149">
-        <v>11.0663077</v>
-      </c>
-      <c r="B149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>goa</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150">
-        <v>51.99239952</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>ebs</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151">
-        <v>348.86474195</v>
-      </c>
-      <c r="B151">
-        <v>327.06926123</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>81.88525613</v>
-      </c>
-      <c r="E151">
-        <v>173.1784255</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>coastwide</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>8682</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152">
-        <v>99.70258392</v>
-      </c>
-      <c r="B152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="E152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>cc _iphc</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>6324</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153">
-        <v>99.10795484</v>
-      </c>
-      <c r="B153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>bc _iphc</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B154">
-        <v>115.19666281</v>
-      </c>
-      <c r="C154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D154">
-        <v>10.27340578</v>
-      </c>
-      <c r="E154">
-        <v>0</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>goa _iphc</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>4622</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>ebs _iphc</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156">
-        <v>541.88061413</v>
-      </c>
-      <c r="B156">
-        <v>485.06655282</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
-      </c>
-      <c r="D156">
-        <v>103.09356334</v>
-      </c>
-      <c r="E156">
-        <v>46.78900873</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>sablefish</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>coastwide _iphc</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>14392</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
         <is>
           <t>4</t>
         </is>
